--- a/Comparativa de Hipótesis.xlsx
+++ b/Comparativa de Hipótesis.xlsx
@@ -12,8 +12,9 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8430"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hipótesis" sheetId="1" r:id="rId1"/>
+    <sheet name="Biblio" sheetId="2" r:id="rId2"/>
+    <sheet name="Event Studies" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
   <si>
     <t>Hipótesis</t>
   </si>
@@ -57,9 +58,6 @@
     <t>Encuentran evidencia de que la polarización reduce la confianza en las instituciones y de que la pérdida de confianza en las instituciones afecta negativamente el SWB</t>
   </si>
   <si>
-    <t xml:space="preserve">Yo encuentro lo mismo. Polarización reduce confianza y confianza aumenta felicidad. </t>
-  </si>
-  <si>
     <t>El efecto es moderado o nulo</t>
   </si>
   <si>
@@ -67,9 +65,6 @@
   </si>
   <si>
     <t>Literatura</t>
-  </si>
-  <si>
-    <t>Ante la polarización se pierde la confianza en las instituciones y eso es lo que afecta al SWB</t>
   </si>
   <si>
     <t>Shanto Iyengar, Yphtach Lelkes, Matthew Levendusky, Neil Malhotra, Sean J. Westwood. 2019. The Origins and Consequences of Affective Polarization in the United States. Annual Review of Political Science 22:129-146. https://doi.org/10.1146/annurev-polisci-051117-073034</t>
@@ -272,22 +267,13 @@
     <t>Lee, S., Choi, J., &amp; Ahn, C. (2025). Hate prompts participation: Examining the dynamic relationship between affective polarization and political participation. Social Media + Society. https://doi.org/10.1177/14614448231177301</t>
   </si>
   <si>
-    <t>La carga emocional, en particular en AL puede aumentar el efecto directo</t>
-  </si>
-  <si>
     <t>Explicación</t>
   </si>
   <si>
     <t>Este es el efecto más consistente de todos. Y un problema en sí mismo para la polarización</t>
   </si>
   <si>
-    <t>La participación política afecta positivamente al SWB. La polarización afecta a los incentivos para la participación o el interés en la política</t>
-  </si>
-  <si>
     <t xml:space="preserve">La relación entre participación y SWB es más clara. La de polarización y participación no lo es tanto. Pero la polarización individual (ideológica) sí. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Participar mejora relaciones con otros y eso aumenta el SWB. Los más felices participan más. Estar convencido de una idea anima a la persona a participar, no así la polarización del ambiente. </t>
   </si>
   <si>
     <t>H5</t>
@@ -303,9 +289,6 @@
     <t>La idea es que el mecanismo de la confianza social es más importante que el mecanismo de la confianza insitucional. La intervención de política conviene por este canal</t>
   </si>
   <si>
-    <t>Baskin, Uygur y Chushak (2026) dicen que los cambios en la democracia pueden no ser suficientemente significativos en los datos observados</t>
-  </si>
-  <si>
     <t>Rudloff, P. (2022). Social trust in polarized times: How perceptions of political polarization affect Americans’ trust in each other. Political Behavior, 44, 1877–1900. https://doi.org/10.1007/s11109-022-09787-1</t>
   </si>
   <si>
@@ -315,15 +298,9 @@
     <t>La polarización política afectiva nacional afecta negativamente el SWB</t>
   </si>
   <si>
-    <t>Yo sí encuentro un vínculo directo negativo.</t>
-  </si>
-  <si>
     <t>No se observa el vínculo con la base a nivel país</t>
   </si>
   <si>
-    <t>Datos propios multilevel</t>
-  </si>
-  <si>
     <t>Granger a nivel país</t>
   </si>
   <si>
@@ -333,23 +310,152 @@
     <t>La evidencia apunta a que la participación anticipa felicidad, pero no al revés</t>
   </si>
   <si>
-    <t>Polarización disminuye confianza. Confianza aumenta SWB y mitiga el efecto.</t>
-  </si>
-  <si>
-    <t>La polarización afecta negativamente la confianza social y eso afecta al SWB. La confianza social ayuda a mitigar el efecto de la caída de la confianza institucional</t>
-  </si>
-  <si>
     <t>La evidencia sostiene H5A pero no H5B</t>
   </si>
   <si>
-    <t>Sí se observa una anticipación débil de polarización a caída en la confianza en las instituciones, pero no de confianza a felicidad</t>
+    <t>La polarización afecta negativamente la confianza social y eso afecta al SWB. La confianza interpersonal ayuda a mitigar el efecto de la caída de la confianza institucional</t>
+  </si>
+  <si>
+    <t>Shock en Polarización</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Pareciera haber una caída en la confianza institucional, pero que de alguna manera ya estaba presente antes del evento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masivas protestas populares en varias ciudades de Brasil, destacando la toma de los tejados del Congreso Nacional en Brasilia por cientos de manifestantes.  Las marchas comenzaron en contra del aumento de las tarifas del transporte público, pero rápidamente sumaron demandas por mayor inversión estatal en salud y educación, así como el rechazo al multimillonario gasto público destinado a la Copa Confederaciones 2013 y al Mundial de Fútbol. </t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Perú</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Se celebró la segunda vuelta de las elecciones presidenciales, un proceso electoral histórico en el que Iván Duque Márquez resultó elegido presidente de la República para el período 2018-2022.</t>
+  </si>
+  <si>
+    <t>Apenas una breve caída en la confianza institucional</t>
+  </si>
+  <si>
+    <t>Segunda vuelta presidencial. Al cierre de las votaciones se dio un empate técnico muy estrecho. Recién el 09/06/2018 se completó el procesamiento de actas que dieron por ganador a Kuczynski (derrotando a Fujimori)</t>
+  </si>
+  <si>
+    <t>No muy clara caída en la confianza institucional</t>
+  </si>
+  <si>
+    <t>El Consejo Nacional Electoral (CNE) de Venezuela anunció oficialmente que la oposición había recolectado las firmas suficientes para activar el referéndum revocatorio contra el presidente Hugo Chávez. El clima político del país escaló fuertemente en tensiones.</t>
+  </si>
+  <si>
+    <t>No muy claro efecto de caída en la satisfacción con la vida y en la confianza interpersonal.</t>
+  </si>
+  <si>
+    <t>Pooled</t>
+  </si>
+  <si>
+    <t>Shock en Interés en Política</t>
+  </si>
+  <si>
+    <t>Promulgación de la Ley 1908 de 2018 por parte del Congreso de la República, diseñada específicamente para fortalecer la investigación y judicialización de organizaciones criminales .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aumento en la confianza institucional, aunque ya se observaba en días anteriores. </t>
+  </si>
+  <si>
+    <t>Se celebró el Referéndum Constitucional. La ciudadanía aprobó la actual Constitución de la República del Ecuador con más del 63% de los votos a favor.</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si bien se observa un aumento en confianza institucional el estudio no es limpio porque los días anteriores también tienen coeficiente positivo. </t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Shock en Felicidad</t>
+  </si>
+  <si>
+    <t>Un fuerte sismo de magnitud entre 6.5 y 6.9 sacudió el sur de Ecuador y el norte de Perú</t>
+  </si>
+  <si>
+    <t>Un fuerte sismo de magnitud 6.5 sacudió la costa del Pacífico</t>
+  </si>
+  <si>
+    <t>Breve aumento en la satisfacción con la vida y de caída en la confianza institucional</t>
+  </si>
+  <si>
+    <t>Breve aumento en la satisfacción con la vida, y en la confianza interpersonal. No muy clara caída en la confianza institucional</t>
+  </si>
+  <si>
+    <t>El efecto más claro es un aumento de la confianza interpersonal</t>
+  </si>
+  <si>
+    <t>Event Study</t>
+  </si>
+  <si>
+    <t>No se encuentra un impacto directo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se observa para confianza institucional un claro impacto negativo, y para Interés en política un efecto negativo no tan claro. </t>
+  </si>
+  <si>
+    <t>No hay evidencia que respalde H5</t>
+  </si>
+  <si>
+    <t>No se observa evidencia que respalde H4A. Se observa un no tan claro respaldo de H4B.</t>
+  </si>
+  <si>
+    <t>Datos multilevel</t>
+  </si>
+  <si>
+    <t>Se observa un vínculo directo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La evidencia sostiene H2. Polarización reduce confianza y confianza aumenta felicidad. </t>
+  </si>
+  <si>
+    <t>Polarización se relaciona nagativamente con confianza interpersonal. Confianza inerpersonal aumenta SWB y mitiga el efecto.</t>
+  </si>
+  <si>
+    <t>La evidencia respalda H2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La carga emocional, en particular en AL puede aumentar el efecto directo. El vínculo si existe no es claro. </t>
+  </si>
+  <si>
+    <t>Resplado débil de H2A, pero no de H2B</t>
+  </si>
+  <si>
+    <t>Los cambios en la democracia pueden no ser suficientemente significativos en los datos observados</t>
+  </si>
+  <si>
+    <t>H2A: Ante la polarización se pierde la confianza en las instituciones y H2B: eso es lo que afecta al SWB</t>
+  </si>
+  <si>
+    <t>H4A: El interés en política afecta positivamente al SWB. H4B: La polarización afecta a los incentivos para la participación o el interés en la política</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participar mejora relaciones con otros y eso aumenta el SWB. Los más felices participan más. Tener una idea más extrema anima a la persona a participar, no así la polarización del ambiente. </t>
+  </si>
+  <si>
+    <t>H4B</t>
+  </si>
+  <si>
+    <t>H4A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,6 +482,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -385,7 +499,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -408,17 +522,106 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -700,273 +903,537 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="51.7109375" customWidth="1"/>
-    <col min="7" max="7" width="39.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="4" customWidth="1"/>
+    <col min="8" max="8" width="51.7109375" customWidth="1"/>
+    <col min="9" max="9" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" customHeight="1">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="66" customHeight="1">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="66" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="77.25" customHeight="1">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="77.25" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="67.5" customHeight="1">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="63" customHeight="1">
+      <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="78" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="81" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="80.25" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="69" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="I6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="198.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="12"/>
+      <c r="B2" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="12"/>
+      <c r="B3" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75">
+      <c r="A4" s="12"/>
+      <c r="B4" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.75">
-      <c r="A4" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="13"/>
+      <c r="B8" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="12"/>
+      <c r="B11" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="13"/>
+      <c r="B12" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="12"/>
+      <c r="B15" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="12"/>
+      <c r="B16" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="13"/>
+      <c r="B17" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="12"/>
+      <c r="B20" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="13"/>
+      <c r="B21" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>46</v>
+    <row r="24" spans="1:2">
+      <c r="A24" s="12"/>
+      <c r="B24" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="13"/>
+      <c r="B25" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A1:A5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="139.140625" customWidth="1"/>
+    <col min="5" max="5" width="42.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="52.5" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="5">
+        <v>41442</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="33" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="5">
+        <v>43268</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="33.75" customHeight="1">
+      <c r="A3" s="4"/>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="5">
+        <v>43256</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="35.25" customHeight="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="5">
+        <v>38141</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="21" customHeight="1">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5">
+        <v>43290</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="5">
+        <v>39719</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20.25" customHeight="1">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" ht="35.25" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="5">
+        <v>45003</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="49.5" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="5">
+        <v>41440</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29.25" customHeight="1">
+      <c r="A11" s="4"/>
+      <c r="B11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="C11:E11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Comparativa de Hipótesis.xlsx
+++ b/Comparativa de Hipótesis.xlsx
@@ -9,12 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8430" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Hipótesis" sheetId="1" r:id="rId1"/>
     <sheet name="Biblio" sheetId="2" r:id="rId2"/>
     <sheet name="Event Studies" sheetId="3" r:id="rId3"/>
+    <sheet name="Event Studies (2)" sheetId="4" r:id="rId4"/>
+    <sheet name="Eventos" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="131">
   <si>
     <t>Hipótesis</t>
   </si>
@@ -56,9 +58,6 @@
   </si>
   <si>
     <t>Encuentran evidencia de que la polarización reduce la confianza en las instituciones y de que la pérdida de confianza en las instituciones afecta negativamente el SWB</t>
-  </si>
-  <si>
-    <t>El efecto es moderado o nulo</t>
   </si>
   <si>
     <t>-</t>
@@ -307,15 +306,9 @@
     <t>La evidencia no respalda la hipótesis</t>
   </si>
   <si>
-    <t>La evidencia apunta a que la participación anticipa felicidad, pero no al revés</t>
-  </si>
-  <si>
     <t>La evidencia sostiene H5A pero no H5B</t>
   </si>
   <si>
-    <t>La polarización afecta negativamente la confianza social y eso afecta al SWB. La confianza interpersonal ayuda a mitigar el efecto de la caída de la confianza institucional</t>
-  </si>
-  <si>
     <t>Shock en Polarización</t>
   </si>
   <si>
@@ -406,9 +399,6 @@
     <t xml:space="preserve">Se observa para confianza institucional un claro impacto negativo, y para Interés en política un efecto negativo no tan claro. </t>
   </si>
   <si>
-    <t>No hay evidencia que respalde H5</t>
-  </si>
-  <si>
     <t>No se observa evidencia que respalde H4A. Se observa un no tan claro respaldo de H4B.</t>
   </si>
   <si>
@@ -421,15 +411,9 @@
     <t xml:space="preserve">La evidencia sostiene H2. Polarización reduce confianza y confianza aumenta felicidad. </t>
   </si>
   <si>
-    <t>Polarización se relaciona nagativamente con confianza interpersonal. Confianza inerpersonal aumenta SWB y mitiga el efecto.</t>
-  </si>
-  <si>
     <t>La evidencia respalda H2A</t>
   </si>
   <si>
-    <t xml:space="preserve">La carga emocional, en particular en AL puede aumentar el efecto directo. El vínculo si existe no es claro. </t>
-  </si>
-  <si>
     <t>Resplado débil de H2A, pero no de H2B</t>
   </si>
   <si>
@@ -449,6 +433,138 @@
   </si>
   <si>
     <t>H4A</t>
+  </si>
+  <si>
+    <t>La relación es moderada o nula.</t>
+  </si>
+  <si>
+    <t>La evidencia apunta a sostener H4A</t>
+  </si>
+  <si>
+    <t>H5A: La polarización afecta negativamente la confianza social y eso afecta al SWB. H5B: La confianza interpersonal ayuda a mitigar el efecto de la caída de la confianza institucional</t>
+  </si>
+  <si>
+    <t>No hay evidencia que respalde H5A</t>
+  </si>
+  <si>
+    <t>Polarización se relaciona negativamente con confianza interpersonal. Confianza inerpersonal aumenta SWB y mitiga el efecto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El vínculo si existe, no es claro. </t>
+  </si>
+  <si>
+    <t>Shock en Polarización (Cherry Picking)</t>
+  </si>
+  <si>
+    <t>Elecciones</t>
+  </si>
+  <si>
+    <t>LLMs</t>
+  </si>
+  <si>
+    <t>Presidente</t>
+  </si>
+  <si>
+    <t>Asamblea Nacional</t>
+  </si>
+  <si>
+    <t>Referendum</t>
+  </si>
+  <si>
+    <t>Base del IFES. ¿Tiene sentido elecciones? No todas las elecciones son polarizantes. El Pool no muestra ningún impacto en ninguna variable</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Segunda vuelta de las elecciones presidenciales</t>
+  </si>
+  <si>
+    <t>Ola de bloqueos de carreteras y protestas violentas</t>
+  </si>
+  <si>
+    <t>Aprobación exprés y opaca del presupuesto</t>
+  </si>
+  <si>
+    <t>Elección de los miembros de la Asamblea Nacional</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>On 8 March 2023, in San Pedro de Atacama (Antofagasta), thousands of women and LGBT+ community members marched at the main square to demand women's rights, the end of gender violence and discrimination against indigenous women, immigrant women and LGBT+ communities in the context of International Women's day</t>
+  </si>
+  <si>
+    <t>On 8 March 2023, in Montevideo (Montevideo), thousands of women marched from Libertad square as part of a demonstration in the context of International Women's day. They called for equality and an end to violence against women, among other demands. The groups Women in Black, Uruguayan Federation of Cooperatives for Mutual Aid, Where are Our Gurisas and Expresas Politicas participated in the march. The mayor of Montevideo (who is part of FA) and the City Director of Culture also took part in the action. The demonstrators burned their banners in front of the University of the Republic.</t>
+  </si>
+  <si>
+    <t>ACLED</t>
+  </si>
+  <si>
+    <t>Solo tiene datos de 2019 en adelante. El pool muestra apenas una caida corta no muy limpia en satisfacción con la vida</t>
+  </si>
+  <si>
+    <t>Otros</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Base Elecciones</t>
+  </si>
+  <si>
+    <t>LLM</t>
+  </si>
+  <si>
+    <t>Base Protestas</t>
+  </si>
+  <si>
+    <t>Jornada de violencia extrema (Jueves negro)</t>
+  </si>
+  <si>
+    <t>Escalada de protestas, tomas de instituciones (Masacre de Pando)</t>
+  </si>
+  <si>
+    <t>Se le pide a un LLM (gemini-3.5-flash-lite) con temperture=0 que identifique eventos polarizantes. El modelo devuelve 161 eventos. Se observa una caída en la confianza en las instituciones. Se chequeó a mano la existencia y relevancia de los 6 eventos coincidentes</t>
+  </si>
+  <si>
+    <t>LLMs 2</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Crisis política y enfrentamientos violentos en el departamento de Pando.</t>
+  </si>
+  <si>
+    <t>Movilizaciones masivas bajo el lema 'El INE no se toca', marcando una ruptura abierta entre el gobierno de López Obrador y sectores de la sociedad civil y oposición.</t>
+  </si>
+  <si>
+    <t>Elección de la Asamblea Nacional Constituyente en medio de protestas masivas y crisis institucional.</t>
+  </si>
+  <si>
+    <t>Las protestas masivas de junio de 2013 marcaron el inicio de una ruptura social y política, exponiendo el descontento con la clase política tradicional y polarizando la opinión pública sobre el modelo de gestión del PT.</t>
+  </si>
+  <si>
+    <t>LLM 2</t>
+  </si>
+  <si>
+    <t>Elecciones extremadamente reñidas que profundizaron la fractura social y política entre los sectores que apoyaban el legado de Fujimori y los que lo rechazaban.</t>
+  </si>
+  <si>
+    <t>Crisis política aguda que resultó en la destitución presidencial y una ola de protestas nacionales con represión policial.</t>
+  </si>
+  <si>
+    <t>En vez de pertmitir que el modelo busque en todas las fechas, se le informa las fechas específicas de las ventanas de latinobarómetro. Caida en confianza institucional y en percepción económica del país</t>
   </si>
 </sst>
 </file>
@@ -499,7 +615,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -584,11 +700,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -597,12 +776,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -614,6 +787,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -622,6 +801,46 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -919,156 +1138,156 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>12</v>
+      <c r="C1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="66" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="77.25" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="63" customHeight="1">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="78" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="80.25" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="80.25" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1098,32 +1317,32 @@
       <c r="A1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>13</v>
+      <c r="B1" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="12"/>
-      <c r="B2" s="9" t="s">
-        <v>16</v>
+      <c r="B2" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="12"/>
-      <c r="B3" s="9" t="s">
-        <v>14</v>
+      <c r="B3" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" s="12"/>
-      <c r="B4" s="9" t="s">
-        <v>15</v>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="13"/>
-      <c r="B5" s="10" t="s">
-        <v>21</v>
+      <c r="B5" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1133,14 +1352,14 @@
       <c r="A7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>18</v>
+      <c r="B7" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="13"/>
-      <c r="B8" s="10" t="s">
-        <v>19</v>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1150,20 +1369,20 @@
       <c r="A10" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>22</v>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="12"/>
-      <c r="B11" s="9" t="s">
-        <v>24</v>
+      <c r="B11" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="13"/>
-      <c r="B12" s="10" t="s">
-        <v>19</v>
+      <c r="B12" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1171,28 +1390,28 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>27</v>
+        <v>86</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="12"/>
-      <c r="B15" s="9" t="s">
-        <v>26</v>
+      <c r="B15" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="12"/>
-      <c r="B16" s="9" t="s">
-        <v>25</v>
+      <c r="B16" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="13"/>
-      <c r="B17" s="10" t="s">
-        <v>28</v>
+      <c r="B17" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1200,22 +1419,22 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>28</v>
+        <v>85</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="12"/>
-      <c r="B20" s="9" t="s">
-        <v>31</v>
+      <c r="B20" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="13"/>
-      <c r="B21" s="10" t="s">
-        <v>30</v>
+      <c r="B21" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1223,32 +1442,32 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>17</v>
+        <v>34</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="12"/>
-      <c r="B24" s="9" t="s">
-        <v>39</v>
+      <c r="B24" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="13"/>
-      <c r="B25" s="10" t="s">
-        <v>40</v>
+      <c r="B25" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A1:A5"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A1:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1262,168 +1481,168 @@
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" customWidth="1"/>
-    <col min="4" max="4" width="139.140625" customWidth="1"/>
+    <col min="4" max="4" width="90.140625" customWidth="1"/>
     <col min="5" max="5" width="42.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="52.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" ht="79.5" customHeight="1">
+      <c r="A1" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4">
+        <v>41442</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="33.75" customHeight="1">
+      <c r="A2" s="14"/>
+      <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="5">
-        <v>41442</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C2" s="4">
+        <v>43268</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="48" customHeight="1">
+      <c r="A3" s="14"/>
+      <c r="B3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4">
+        <v>42526</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="48" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="33" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="5">
-        <v>43268</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C4" s="4">
+        <v>38141</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="33.75" customHeight="1">
-      <c r="A3" s="4"/>
-      <c r="B3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="5">
-        <v>43256</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="21" customHeight="1">
+      <c r="A5" s="14"/>
+      <c r="B5" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="35.25" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="5">
-        <v>38141</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" spans="1:5" ht="33.75" customHeight="1">
+      <c r="A6" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4">
+        <v>43290</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="21" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" ht="36" customHeight="1">
-      <c r="A6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A7" s="14"/>
+      <c r="B7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="4">
+        <v>39719</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="5">
-        <v>43290</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A8" s="14"/>
+      <c r="B8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+    </row>
+    <row r="9" spans="1:5" ht="30">
+      <c r="A9" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="36" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="5">
-        <v>39719</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C9" s="4">
+        <v>45003</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="45">
+      <c r="A10" s="14"/>
+      <c r="B10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="20.25" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" ht="35.25" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="5">
-        <v>45003</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C10" s="4">
+        <v>41440</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="49.5" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="5">
-        <v>41440</v>
-      </c>
-      <c r="D10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="27" customHeight="1">
+      <c r="A11" s="14"/>
+      <c r="B11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1436,4 +1655,760 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="90.140625" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="79.5" customHeight="1">
+      <c r="A1" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="10">
+        <v>41442</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="33.75" customHeight="1">
+      <c r="A2" s="14"/>
+      <c r="B2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="10">
+        <v>43268</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="48" customHeight="1">
+      <c r="A3" s="14"/>
+      <c r="B3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="10">
+        <v>42526</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="48" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="10">
+        <v>38141</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="21" customHeight="1">
+      <c r="A5" s="14"/>
+      <c r="B5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="10">
+        <v>39019</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="19"/>
+      <c r="B7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="10">
+        <v>43268</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="19"/>
+      <c r="B8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="10">
+        <v>39005</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="22"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="19"/>
+      <c r="B9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="10">
+        <v>39719</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="22"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="19"/>
+      <c r="B10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="10">
+        <v>42526</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="22"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="19"/>
+      <c r="B11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="10">
+        <v>40447</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="17"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="19"/>
+      <c r="B12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="10">
+        <v>44171</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="17"/>
+    </row>
+    <row r="13" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A13" s="20"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="10">
+        <v>39702</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="17"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="14"/>
+      <c r="B15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="10">
+        <v>43268</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="17"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="10">
+        <v>44109</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="17"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="14"/>
+      <c r="B17" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="10">
+        <v>37826</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="17"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="14"/>
+      <c r="B18" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="10">
+        <v>44156</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="14"/>
+      <c r="B19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="10">
+        <v>42946</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="17"/>
+    </row>
+    <row r="20" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+    </row>
+    <row r="21" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A21" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="10">
+        <v>39702</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="17"/>
+    </row>
+    <row r="22" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A22" s="14"/>
+      <c r="B22" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="10">
+        <v>41445</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="17"/>
+    </row>
+    <row r="23" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A23" s="14"/>
+      <c r="B23" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="10">
+        <v>44983</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" s="17"/>
+    </row>
+    <row r="24" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="10">
+        <v>42526</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="17"/>
+    </row>
+    <row r="25" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A25" s="14"/>
+      <c r="B25" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="10">
+        <v>44145</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="17"/>
+    </row>
+    <row r="26" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A26" s="14"/>
+      <c r="B26" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="10">
+        <v>42946</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="17"/>
+    </row>
+    <row r="27" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A27" s="14"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+    </row>
+    <row r="28" spans="1:5" ht="48.75" customHeight="1">
+      <c r="A28" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="10">
+        <v>44993</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="17"/>
+    </row>
+    <row r="29" spans="1:5" ht="76.5" customHeight="1">
+      <c r="A29" s="14"/>
+      <c r="B29" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="10">
+        <v>44993</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="17"/>
+    </row>
+    <row r="30" spans="1:5" ht="27" customHeight="1">
+      <c r="A30" s="14"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D6:E6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="8" width="4.42578125" style="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="78">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8">
+      <c r="B2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="10">
+        <v>41442</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="10">
+        <v>43268</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="10">
+        <v>42526</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="27"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="10">
+        <v>38141</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="10">
+        <v>39019</v>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="10">
+        <v>39005</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="10">
+        <v>39719</v>
+      </c>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="10">
+        <v>40447</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="10">
+        <v>44171</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="10">
+        <v>39702</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" s="27"/>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="10">
+        <v>44109</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="10">
+        <v>37826</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="10">
+        <v>44156</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="10">
+        <v>44145</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="27"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="10">
+        <v>42946</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="27"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="10">
+        <v>44983</v>
+      </c>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="27"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="10">
+        <v>44993</v>
+      </c>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="10">
+        <v>44993</v>
+      </c>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Comparativa de Hipótesis.xlsx
+++ b/Comparativa de Hipótesis.xlsx
@@ -453,9 +453,6 @@
     <t xml:space="preserve">El vínculo si existe, no es claro. </t>
   </si>
   <si>
-    <t>Shock en Polarización (Cherry Picking)</t>
-  </si>
-  <si>
     <t>Elecciones</t>
   </si>
   <si>
@@ -565,6 +562,9 @@
   </si>
   <si>
     <t>En vez de pertmitir que el modelo busque en todas las fechas, se le informa las fechas específicas de las ventanas de latinobarómetro. Caida en confianza institucional y en percepción económica del país</t>
+  </si>
+  <si>
+    <t>Shock en Polarización (no algorítmico)</t>
   </si>
 </sst>
 </file>
@@ -793,6 +793,16 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -814,6 +824,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -828,19 +841,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1314,7 +1314,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -1322,25 +1322,25 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="12"/>
+      <c r="A2" s="16"/>
       <c r="B2" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="12"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
-      <c r="A4" s="12"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="13"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="8" t="s">
         <v>20</v>
       </c>
@@ -1349,7 +1349,7 @@
       <c r="A6" s="3"/>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="15" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1357,7 +1357,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="13"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="8" t="s">
         <v>18</v>
       </c>
@@ -1366,7 +1366,7 @@
       <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="15" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1374,13 +1374,13 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="13"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="8" t="s">
         <v>18</v>
       </c>
@@ -1389,7 +1389,7 @@
       <c r="A13" s="3"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="15" t="s">
         <v>86</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1397,19 +1397,19 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="12"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="12"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="13"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="8" t="s">
         <v>27</v>
       </c>
@@ -1418,7 +1418,7 @@
       <c r="A18" s="3"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="15" t="s">
         <v>85</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -1426,13 +1426,13 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="12"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="13"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="8" t="s">
         <v>29</v>
       </c>
@@ -1441,7 +1441,7 @@
       <c r="A22" s="3"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -1449,13 +1449,13 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="12"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="13"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="8" t="s">
         <v>39</v>
       </c>
@@ -1486,7 +1486,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="79.5" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1503,7 +1503,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="33.75" customHeight="1">
-      <c r="A2" s="14"/>
+      <c r="A2" s="18"/>
       <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
@@ -1518,7 +1518,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="48" customHeight="1">
-      <c r="A3" s="14"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="2" t="s">
         <v>50</v>
       </c>
@@ -1533,7 +1533,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="48" customHeight="1">
-      <c r="A4" s="14"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
@@ -1548,18 +1548,18 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="21" customHeight="1">
-      <c r="A5" s="14"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" ht="33.75" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="18" t="s">
         <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1576,7 +1576,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A7" s="14"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="2" t="s">
         <v>63</v>
       </c>
@@ -1591,18 +1591,18 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A8" s="14"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" ht="30">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="18" t="s">
         <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1619,7 +1619,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="45">
-      <c r="A10" s="14"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
       </c>
@@ -1634,15 +1634,15 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="27" customHeight="1">
-      <c r="A11" s="14"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1670,8 +1670,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="79.5" customHeight="1">
-      <c r="A1" s="14" t="s">
-        <v>93</v>
+      <c r="A1" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>46</v>
@@ -1687,7 +1687,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="33.75" customHeight="1">
-      <c r="A2" s="14"/>
+      <c r="A2" s="18"/>
       <c r="B2" s="9" t="s">
         <v>49</v>
       </c>
@@ -1702,7 +1702,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="48" customHeight="1">
-      <c r="A3" s="14"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="9" t="s">
         <v>50</v>
       </c>
@@ -1717,7 +1717,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="48" customHeight="1">
-      <c r="A4" s="14"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="9" t="s">
         <v>51</v>
       </c>
@@ -1732,19 +1732,19 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="21" customHeight="1">
-      <c r="A5" s="14"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="18" t="s">
-        <v>94</v>
+      <c r="A6" s="23" t="s">
+        <v>93</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>46</v>
@@ -1752,327 +1752,324 @@
       <c r="C6" s="10">
         <v>39019</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="22"/>
+      <c r="D6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="19"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="10">
         <v>43268</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="22"/>
+      <c r="D7" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="19"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="10">
         <v>39005</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="22"/>
+      <c r="D8" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="27"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="19"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="10">
         <v>39719</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="22"/>
+      <c r="D9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="27"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="19"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="10">
         <v>42526</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="22"/>
+      <c r="D10" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="27"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="19"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="10">
         <v>40447</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="17"/>
+      <c r="D11" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="21"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="19"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="10">
         <v>44171</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="17"/>
+      <c r="D12" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="21"/>
     </row>
     <row r="13" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A13" s="20"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C14" s="10">
         <v>39702</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" s="17"/>
+      <c r="D14" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="14"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="10">
         <v>43268</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="17"/>
+      <c r="D15" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="14"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" s="10">
         <v>44109</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" s="17"/>
+      <c r="D16" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="14"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C17" s="10">
         <v>37826</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="17"/>
+      <c r="D17" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="14"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C18" s="10">
         <v>44156</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" s="17"/>
+      <c r="D18" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="14"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="10">
         <v>42946</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="17"/>
+      <c r="D19" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A20" s="14"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+    </row>
+    <row r="21" spans="1:5" ht="31.5" customHeight="1">
+      <c r="A21" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-    </row>
-    <row r="21" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>121</v>
-      </c>
       <c r="B21" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" s="10">
         <v>39702</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="17"/>
+      <c r="D21" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A22" s="14"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C22" s="10">
         <v>41445</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" s="17"/>
+      <c r="D22" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A23" s="14"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C23" s="10">
         <v>44983</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" s="17"/>
+      <c r="D23" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A24" s="14"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="10">
         <v>42526</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" s="17"/>
+      <c r="D24" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A25" s="14"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="10">
         <v>44145</v>
       </c>
-      <c r="D25" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" s="17"/>
+      <c r="D25" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A26" s="14"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="10">
         <v>42946</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="17"/>
+      <c r="D26" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" s="21"/>
     </row>
     <row r="27" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A27" s="14"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
+      <c r="C27" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
     </row>
     <row r="28" spans="1:5" ht="48.75" customHeight="1">
-      <c r="A28" s="14" t="s">
-        <v>111</v>
+      <c r="A28" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C28" s="10">
         <v>44993</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="17"/>
+      <c r="D28" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="21"/>
     </row>
     <row r="29" spans="1:5" ht="76.5" customHeight="1">
-      <c r="A29" s="14"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" s="10">
         <v>44993</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29" s="17"/>
+      <c r="D29" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="21"/>
     </row>
     <row r="30" spans="1:5" ht="27" customHeight="1">
-      <c r="A30" s="14"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
+      <c r="C30" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="A21:A27"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D6:E6"/>
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="D11:E11"/>
@@ -2083,15 +2080,18 @@
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2102,26 +2102,26 @@
   <dimension ref="B1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="8" width="4.42578125" style="24" customWidth="1"/>
+    <col min="4" max="8" width="4.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="78">
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E1" s="26" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="G1" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>116</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="2:8">
@@ -2131,15 +2131,15 @@
       <c r="C2" s="10">
         <v>41442</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" s="27"/>
+      <c r="D2" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="14"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="9" t="s">
@@ -2148,17 +2148,17 @@
       <c r="C3" s="10">
         <v>43268</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+      <c r="D3" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="9" t="s">
@@ -2167,17 +2167,17 @@
       <c r="C4" s="10">
         <v>42526</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="H4" s="27"/>
+      <c r="D4" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="14"/>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="9" t="s">
@@ -2186,13 +2186,13 @@
       <c r="C5" s="10">
         <v>38141</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
+      <c r="D5" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="9" t="s">
@@ -2201,13 +2201,13 @@
       <c r="C6" s="10">
         <v>39019</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="9" t="s">
@@ -2216,13 +2216,13 @@
       <c r="C7" s="10">
         <v>39005</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="9" t="s">
@@ -2231,13 +2231,13 @@
       <c r="C8" s="10">
         <v>39719</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="9" t="s">
@@ -2246,13 +2246,13 @@
       <c r="C9" s="10">
         <v>40447</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="9" t="s">
@@ -2261,75 +2261,75 @@
       <c r="C10" s="10">
         <v>44171</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" s="10">
         <v>39702</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="H11" s="27"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="14"/>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C12" s="10">
         <v>44109</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" s="10">
         <v>37826</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="10">
         <v>44156</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="9" t="s">
@@ -2338,13 +2338,13 @@
       <c r="C15" s="10">
         <v>44145</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="H15" s="27"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="14"/>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
@@ -2353,59 +2353,59 @@
       <c r="C16" s="10">
         <v>42946</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="27"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="14"/>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C17" s="10">
         <v>44983</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="H17" s="27"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="14"/>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" s="10">
         <v>44993</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27" t="s">
-        <v>114</v>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" s="10">
         <v>44993</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27" t="s">
-        <v>114</v>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Comparativa de Hipótesis.xlsx
+++ b/Comparativa de Hipótesis.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8430" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8430" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Hipótesis" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="131">
   <si>
     <t>Hipótesis</t>
   </si>
@@ -510,9 +510,6 @@
     <t>Solo tiene datos de 2019 en adelante. El pool muestra apenas una caida corta no muy limpia en satisfacción con la vida</t>
   </si>
   <si>
-    <t>Otros</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -565,6 +562,9 @@
   </si>
   <si>
     <t>Shock en Polarización (no algorítmico)</t>
+  </si>
+  <si>
+    <t>No algorítmico</t>
   </si>
 </sst>
 </file>
@@ -818,13 +818,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -835,12 +841,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1671,7 +1671,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="79.5" customHeight="1">
       <c r="A1" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>46</v>
@@ -1743,7 +1743,7 @@
       <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="25" t="s">
         <v>93</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -1752,91 +1752,91 @@
       <c r="C6" s="10">
         <v>39019</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="24"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="10">
         <v>43268</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="27"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="24"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="10">
         <v>39005</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="24"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="10">
         <v>39719</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="27"/>
+      <c r="E9" s="22"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="24"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="10">
         <v>42526</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="22"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="24"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="10">
         <v>40447</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="24"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="24"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="10">
         <v>44171</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="24"/>
     </row>
     <row r="13" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A13" s="25"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="9"/>
       <c r="C13" s="19" t="s">
         <v>98</v>
@@ -1854,10 +1854,10 @@
       <c r="C14" s="10">
         <v>39702</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="21"/>
+      <c r="D14" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="24"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="18"/>
@@ -1867,10 +1867,10 @@
       <c r="C15" s="10">
         <v>43268</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="24"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="18"/>
@@ -1880,10 +1880,10 @@
       <c r="C16" s="10">
         <v>44109</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="24"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="18"/>
@@ -1893,10 +1893,10 @@
       <c r="C17" s="10">
         <v>37826</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="21"/>
+      <c r="D17" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="24"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="18"/>
@@ -1906,10 +1906,10 @@
       <c r="C18" s="10">
         <v>44156</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="24"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="18"/>
@@ -1919,23 +1919,23 @@
       <c r="C19" s="10">
         <v>42946</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="24"/>
     </row>
     <row r="20" spans="1:5" ht="31.5" customHeight="1">
       <c r="A20" s="18"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
+      <c r="C20" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
     </row>
     <row r="21" spans="1:5" ht="31.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>99</v>
@@ -1943,10 +1943,10 @@
       <c r="C21" s="10">
         <v>39702</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="21"/>
+      <c r="D21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="24"/>
     </row>
     <row r="22" spans="1:5" ht="31.5" customHeight="1">
       <c r="A22" s="18"/>
@@ -1956,23 +1956,23 @@
       <c r="C22" s="10">
         <v>41445</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="21"/>
+      <c r="D22" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="24"/>
     </row>
     <row r="23" spans="1:5" ht="31.5" customHeight="1">
       <c r="A23" s="18"/>
       <c r="B23" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C23" s="10">
         <v>44983</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E23" s="21"/>
+      <c r="D23" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="24"/>
     </row>
     <row r="24" spans="1:5" ht="31.5" customHeight="1">
       <c r="A24" s="18"/>
@@ -1982,10 +1982,10 @@
       <c r="C24" s="10">
         <v>42526</v>
       </c>
-      <c r="D24" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" s="21"/>
+      <c r="D24" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" s="24"/>
     </row>
     <row r="25" spans="1:5" ht="31.5" customHeight="1">
       <c r="A25" s="18"/>
@@ -1995,10 +1995,10 @@
       <c r="C25" s="10">
         <v>44145</v>
       </c>
-      <c r="D25" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" s="21"/>
+      <c r="D25" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="24"/>
     </row>
     <row r="26" spans="1:5" ht="31.5" customHeight="1">
       <c r="A26" s="18"/>
@@ -2008,19 +2008,19 @@
       <c r="C26" s="10">
         <v>42946</v>
       </c>
-      <c r="D26" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E26" s="21"/>
+      <c r="D26" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" s="24"/>
     </row>
     <row r="27" spans="1:5" ht="31.5" customHeight="1">
       <c r="A27" s="18"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
+      <c r="C27" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
     </row>
     <row r="28" spans="1:5" ht="48.75" customHeight="1">
       <c r="A28" s="18" t="s">
@@ -2032,10 +2032,10 @@
       <c r="C28" s="10">
         <v>44993</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="21"/>
+      <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:5" ht="76.5" customHeight="1">
       <c r="A29" s="18"/>
@@ -2045,10 +2045,10 @@
       <c r="C29" s="10">
         <v>44993</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="21"/>
+      <c r="E29" s="24"/>
     </row>
     <row r="30" spans="1:5" ht="27" customHeight="1">
       <c r="A30" s="18"/>
@@ -2061,15 +2061,12 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="D11:E11"/>
@@ -2086,12 +2083,15 @@
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2109,85 +2109,79 @@
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>115</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="2:8">
       <c r="B2" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C2" s="10">
-        <v>41442</v>
+        <v>43268</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
-      <c r="G2" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="H2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="9" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="C3" s="10">
-        <v>43268</v>
+        <v>39702</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>113</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="9" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" s="10">
-        <v>42526</v>
+        <v>44109</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>113</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E4" s="14"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="14" t="s">
-        <v>113</v>
-      </c>
+      <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="9" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="C5" s="10">
-        <v>38141</v>
+        <v>37826</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
@@ -2196,29 +2190,31 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="9" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C6" s="10">
-        <v>39019</v>
-      </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14" t="s">
-        <v>113</v>
-      </c>
+        <v>44156</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="14"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C7" s="10">
-        <v>39005</v>
-      </c>
-      <c r="D7" s="14"/>
+        <v>42946</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>112</v>
+      </c>
       <c r="E7" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
@@ -2226,14 +2222,14 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="9" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C8" s="10">
-        <v>39719</v>
+        <v>41442</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
@@ -2241,29 +2237,31 @@
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="10">
-        <v>40447</v>
+        <v>42526</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
+      <c r="H9" s="14" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="10">
-        <v>44171</v>
+        <v>44145</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
@@ -2271,141 +2269,137 @@
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="9" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C11" s="10">
-        <v>39702</v>
+        <v>44983</v>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>113</v>
-      </c>
+      <c r="E11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
       <c r="H11" s="14"/>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="9" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C12" s="10">
-        <v>44109</v>
+        <v>44993</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C13" s="10">
-        <v>37826</v>
+        <v>44993</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="9" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="C14" s="10">
-        <v>44156</v>
+        <v>38141</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
-      <c r="F14" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14" t="s">
+        <v>112</v>
+      </c>
       <c r="H14" s="14"/>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C15" s="10">
-        <v>44145</v>
+        <v>39019</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="H15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C16" s="10">
-        <v>42946</v>
+        <v>39005</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
-      <c r="F16" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="H16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="9" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="C17" s="10">
-        <v>44983</v>
+        <v>39719</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
-      <c r="G17" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="H17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="9" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="C18" s="10">
-        <v>44993</v>
+        <v>40447</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
       <c r="H18" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="9" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="C19" s="10">
-        <v>44993</v>
+        <v>44171</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
